--- a/0162A.xlsx
+++ b/0162A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1548567a393db7db/Escritorio/CCH-VALLEJO/Ciclos escolares/2027-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="8_{5C0132DE-4B70-4AAA-BE25-AF782B094B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCF133F4-792A-455B-A2D4-B4A9FD9F2BD8}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="8_{5C0132DE-4B70-4AAA-BE25-AF782B094B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CFF6A94-A8B7-4E53-870D-C70DF04A31E4}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" activeTab="1" xr2:uid="{A5C01852-C15E-47C4-B915-FB1981CD68D0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A5C01852-C15E-47C4-B915-FB1981CD68D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificaciones" sheetId="2" r:id="rId1"/>
@@ -39,8 +39,27 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={AFB3928C-D3E6-4714-8CC6-64884FE4C7D1}</author>
+  </authors>
+  <commentList>
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{AFB3928C-D3E6-4714-8CC6-64884FE4C7D1}">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Justificado por cita de enterga de doc
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="194">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -145,18 +164,6 @@
     <t>Porcentaje de Asistencia</t>
   </si>
   <si>
-    <t>Columna143</t>
-  </si>
-  <si>
-    <t>Columna144</t>
-  </si>
-  <si>
-    <t>Columna145</t>
-  </si>
-  <si>
-    <t>Columna146</t>
-  </si>
-  <si>
     <t>Columna147</t>
   </si>
   <si>
@@ -619,7 +626,22 @@
     <t>jueves, 10, septiembre</t>
   </si>
   <si>
-    <t>Columna1</t>
+    <t>jueves, 17, septiembre</t>
+  </si>
+  <si>
+    <t>viernes, 18, septiembre</t>
+  </si>
+  <si>
+    <t>martes, 29, septiembre</t>
+  </si>
+  <si>
+    <t>lunes, 05, octubre</t>
+  </si>
+  <si>
+    <t>miércoles, 09, septiembre</t>
+  </si>
+  <si>
+    <t>3 preguntas gratis y 1 hora de cuaderno gratis, 0.5decimas en el examen</t>
   </si>
 </sst>
 </file>
@@ -3050,6 +3072,12 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Daniel Rodriguez García" id="{C16CB42A-6BA5-421B-A403-06D25CCDE8A0}" userId="1548567a393db7db" providerId="Windows Live"/>
+</personList>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F8DBE4A-D7BA-4106-9004-184A8D42EE4F}" name="Tabla1" displayName="Tabla1" ref="A1:DE25" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
   <autoFilter ref="A1:DE25" xr:uid="{2D107F7A-B36A-4E9C-BD03-84CE7C3C9C0D}"/>
@@ -3064,11 +3092,11 @@
     <tableColumn id="24" xr3:uid="{DBC8DBA9-7261-4160-9D00-4A3736293EB1}" name="viernes, 04, septiembre" dataDxfId="107"/>
     <tableColumn id="25" xr3:uid="{42C2D190-0902-4782-B9C2-75F8DE047170}" name="martes, 08, septiembre" dataDxfId="106"/>
     <tableColumn id="26" xr3:uid="{FCF96A47-BEDA-468E-AF93-71492B313A59}" name="jueves, 10, septiembre" dataDxfId="105"/>
-    <tableColumn id="39" xr3:uid="{25BA813B-CCEF-4305-B0A7-7FD9981E5115}" name="Columna1" dataDxfId="104"/>
-    <tableColumn id="40" xr3:uid="{4F6D4C1C-9DD1-4724-88AE-2FAC0212ED00}" name="Columna143" dataDxfId="103"/>
-    <tableColumn id="41" xr3:uid="{BD9E4F56-9872-4891-B429-0EFEF2079CFC}" name="Columna144" dataDxfId="102"/>
-    <tableColumn id="42" xr3:uid="{DB4B7182-F11E-4656-8E00-EA9D8A3EF868}" name="Columna145" dataDxfId="101"/>
-    <tableColumn id="43" xr3:uid="{33AFD5C8-013B-40DE-961C-6C7410B13DCF}" name="Columna146" dataDxfId="100"/>
+    <tableColumn id="39" xr3:uid="{25BA813B-CCEF-4305-B0A7-7FD9981E5115}" name="jueves, 17, septiembre" dataDxfId="104"/>
+    <tableColumn id="40" xr3:uid="{4F6D4C1C-9DD1-4724-88AE-2FAC0212ED00}" name="viernes, 18, septiembre" dataDxfId="103"/>
+    <tableColumn id="41" xr3:uid="{BD9E4F56-9872-4891-B429-0EFEF2079CFC}" name="martes, 29, septiembre" dataDxfId="102"/>
+    <tableColumn id="42" xr3:uid="{DB4B7182-F11E-4656-8E00-EA9D8A3EF868}" name="lunes, 05, octubre" dataDxfId="101"/>
+    <tableColumn id="43" xr3:uid="{33AFD5C8-013B-40DE-961C-6C7410B13DCF}" name="miércoles, 09, septiembre" dataDxfId="100"/>
     <tableColumn id="44" xr3:uid="{1E988917-2B87-423F-99FF-4E6AF3743E14}" name="Columna147" dataDxfId="99"/>
     <tableColumn id="45" xr3:uid="{590ED27B-2DA1-46A8-A393-7646B10CC53A}" name="Columna148" dataDxfId="98"/>
     <tableColumn id="46" xr3:uid="{553F7F31-7AAE-4BCE-B509-6DFE52011758}" name="Columna149" dataDxfId="97"/>
@@ -3487,26 +3515,34 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J5" dT="2026-09-17T15:09:37.40" personId="{C16CB42A-6BA5-421B-A403-06D25CCDE8A0}" id="{AFB3928C-D3E6-4714-8CC6-64884FE4C7D1}">
+    <text xml:space="preserve">Justificado por cita de enterga de doc
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2556ABEB-78B5-4BAE-B49D-0F1689057752}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:X45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
     <col min="2" max="2" width="33.36328125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="15" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="8.90625" style="16" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" style="15" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="7.54296875" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="7.90625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="6.54296875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="11.453125" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="6.453125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="7.08984375" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="6.26953125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="8.453125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="8.90625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="8.1796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" customWidth="1"/>
+    <col min="7" max="7" width="7.54296875" customWidth="1"/>
+    <col min="8" max="9" width="7.90625" customWidth="1"/>
+    <col min="10" max="10" width="6.54296875" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" customWidth="1"/>
+    <col min="12" max="13" width="6.453125" customWidth="1"/>
+    <col min="14" max="14" width="7.08984375" customWidth="1"/>
+    <col min="15" max="15" width="6.26953125" customWidth="1"/>
+    <col min="16" max="16" width="8.453125" customWidth="1"/>
     <col min="17" max="18" width="7.36328125" customWidth="1"/>
     <col min="19" max="23" width="11.453125" customWidth="1"/>
     <col min="24" max="25" width="10.7265625" customWidth="1"/>
@@ -3520,16 +3556,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>2</v>
@@ -3562,7 +3598,7 @@
         <v>11</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>12</v>
@@ -3571,13 +3607,13 @@
         <v>13</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="W1" s="7" t="s">
         <v>14</v>
@@ -3591,19 +3627,19 @@
         <v>327254630</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D2" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="10">
         <f>IFERROR(IF(OR(K2="NP",P2="NP",S2="NP",W2="NP"),"NP",K2+P2+S2+W2+X2),0)</f>
-        <v>0</v>
+        <v>2.0356521739130438</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -3613,16 +3649,18 @@
         <f t="shared" ref="K2:K25" si="0">IF(OR(G2="NP", H2="NP", I2="NP"), "NP", ((G2*$E$30/$E$31) + (I2*$E$30/$E$31) + (H2*$E$30/$E$31)+(J2*$E$30/$E$31))/10)</f>
         <v>0</v>
       </c>
-      <c r="L2" s="11"/>
+      <c r="L2" s="11">
+        <v>8</v>
+      </c>
       <c r="M2" s="11"/>
       <c r="N2" s="2"/>
       <c r="O2" s="11">
         <f>SUM(L2:N2)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P2" s="12">
         <f>IFERROR((O2*2)/MAX($O$2:$O$25),0)</f>
-        <v>0</v>
+        <v>0.69565217391304346</v>
       </c>
       <c r="Q2" s="11">
         <v>0</v>
@@ -3635,12 +3673,14 @@
         <f>R2*0.15</f>
         <v>0</v>
       </c>
-      <c r="T2" s="11"/>
+      <c r="T2" s="11">
+        <v>6.7</v>
+      </c>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
       <c r="W2" s="14">
         <f>IFERROR(AVERAGE(T2:V2)*0.2,0)</f>
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X2" s="14"/>
     </row>
@@ -3649,10 +3689,10 @@
         <v>327185172</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D3" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -3661,7 +3701,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="10">
         <f t="shared" ref="F3:F25" si="1">IFERROR(IF(OR(K3="NP",P3="NP",S3="NP",W3="NP"),"NP",K3+P3+S3+W3+X3),0)</f>
-        <v>0</v>
+        <v>1.826086956521739</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
@@ -3671,16 +3711,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="11">
+        <v>21</v>
+      </c>
       <c r="M3" s="11"/>
       <c r="N3" s="2"/>
       <c r="O3" s="11">
         <f t="shared" ref="O3:O25" si="2">SUM(L3:N3)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P3" s="12">
         <f t="shared" ref="P3:P25" si="3">IFERROR((O3*2)/MAX($O$2:$O$25),0)</f>
-        <v>0</v>
+        <v>1.826086956521739</v>
       </c>
       <c r="Q3" s="11">
         <v>0</v>
@@ -3693,7 +3735,9 @@
         <f t="shared" ref="S3:S25" si="5">R3*0.15</f>
         <v>0</v>
       </c>
-      <c r="T3" s="11"/>
+      <c r="T3" s="11">
+        <v>0</v>
+      </c>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
       <c r="W3" s="14">
@@ -3702,19 +3746,19 @@
       </c>
       <c r="X3" s="14"/>
     </row>
-    <row r="4" spans="1:24" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>327031196</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D4" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="10">
@@ -3729,7 +3773,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="11"/>
+      <c r="L4" s="11">
+        <v>0</v>
+      </c>
       <c r="M4" s="11"/>
       <c r="N4" s="2"/>
       <c r="O4" s="11">
@@ -3751,7 +3797,9 @@
         <f t="shared" si="5"/>
         <v>1.155</v>
       </c>
-      <c r="T4" s="11"/>
+      <c r="T4" s="11">
+        <v>0</v>
+      </c>
       <c r="U4" s="11"/>
       <c r="V4" s="11"/>
       <c r="W4" s="14">
@@ -3760,15 +3808,15 @@
       </c>
       <c r="X4" s="14"/>
     </row>
-    <row r="5" spans="1:24" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>327324009</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D5" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -3777,7 +3825,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="10">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>4.84</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -3787,16 +3835,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L5" s="11"/>
+      <c r="L5" s="11">
+        <v>23</v>
+      </c>
       <c r="M5" s="11"/>
       <c r="N5" s="2"/>
       <c r="O5" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P5" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="11">
         <v>10</v>
@@ -3809,12 +3859,14 @@
         <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
-      <c r="T5" s="11"/>
+      <c r="T5" s="11">
+        <v>6.7</v>
+      </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
       <c r="W5" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X5" s="14"/>
     </row>
@@ -3823,19 +3875,19 @@
         <v>327263227</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D6" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.8495652173913044</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -3845,16 +3897,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="11"/>
+      <c r="L6" s="11">
+        <v>10</v>
+      </c>
       <c r="M6" s="11"/>
       <c r="N6" s="2"/>
       <c r="O6" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P6" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="Q6" s="11">
         <v>0</v>
@@ -3867,12 +3921,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T6" s="11"/>
+      <c r="T6" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
       <c r="W6" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="X6" s="14"/>
     </row>
@@ -3881,10 +3937,10 @@
         <v>327038432</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D7" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -3893,7 +3949,7 @@
       <c r="E7" s="9"/>
       <c r="F7" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.905217391304348</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -3903,16 +3959,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="11"/>
+      <c r="L7" s="11">
+        <v>18</v>
+      </c>
       <c r="M7" s="11"/>
       <c r="N7" s="2"/>
       <c r="O7" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P7" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.5652173913043479</v>
       </c>
       <c r="Q7" s="11">
         <v>0</v>
@@ -3925,12 +3983,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T7" s="11"/>
+      <c r="T7" s="11">
+        <v>6.7</v>
+      </c>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
       <c r="W7" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X7" s="14"/>
     </row>
@@ -3939,10 +3999,10 @@
         <v>327491192</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D8" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -3951,7 +4011,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="10">
         <f t="shared" si="1"/>
-        <v>0.79499999999999993</v>
+        <v>3.5141304347826083</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -3961,16 +4021,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L8" s="11"/>
+      <c r="L8" s="11">
+        <v>20</v>
+      </c>
       <c r="M8" s="11"/>
       <c r="N8" s="2"/>
       <c r="O8" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.7391304347826086</v>
       </c>
       <c r="Q8" s="11">
         <v>5.3</v>
@@ -3983,33 +4045,35 @@
         <f t="shared" si="5"/>
         <v>0.79499999999999993</v>
       </c>
-      <c r="T8" s="11"/>
+      <c r="T8" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
       <c r="W8" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="X8" s="14"/>
     </row>
-    <row r="9" spans="1:24" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>327310675</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D9" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="10">
         <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>3.6052173913043477</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -4019,16 +4083,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L9" s="11"/>
+      <c r="L9" s="11">
+        <v>18</v>
+      </c>
       <c r="M9" s="11"/>
       <c r="N9" s="2"/>
       <c r="O9" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.5652173913043479</v>
       </c>
       <c r="Q9" s="11">
         <v>8</v>
@@ -4041,33 +4107,35 @@
         <f t="shared" si="5"/>
         <v>1.2</v>
       </c>
-      <c r="T9" s="11"/>
+      <c r="T9" s="11">
+        <v>4.2</v>
+      </c>
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
       <c r="W9" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="X9" s="14"/>
     </row>
-    <row r="10" spans="1:24" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>327331829</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D10" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="10">
         <f t="shared" si="1"/>
-        <v>1.2899999999999998</v>
+        <v>3.6082608695652167</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
@@ -4077,16 +4145,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="11"/>
+      <c r="L10" s="11">
+        <v>17</v>
+      </c>
       <c r="M10" s="11"/>
       <c r="N10" s="2"/>
       <c r="O10" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P10" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.4782608695652173</v>
       </c>
       <c r="Q10" s="11">
         <v>8.6</v>
@@ -4099,33 +4169,35 @@
         <f t="shared" si="5"/>
         <v>1.2899999999999998</v>
       </c>
-      <c r="T10" s="11"/>
+      <c r="T10" s="11">
+        <v>4.2</v>
+      </c>
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
       <c r="W10" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="X10" s="14"/>
     </row>
-    <row r="11" spans="1:24" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>327216986</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D11" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="10">
         <f t="shared" si="1"/>
-        <v>1.44</v>
+        <v>3.149565217391304</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
@@ -4135,16 +4207,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="11">
+        <v>10</v>
+      </c>
       <c r="M11" s="11"/>
       <c r="N11" s="2"/>
       <c r="O11" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P11" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="Q11" s="11">
         <v>9.6</v>
@@ -4157,12 +4231,14 @@
         <f t="shared" si="5"/>
         <v>1.44</v>
       </c>
-      <c r="T11" s="11"/>
+      <c r="T11" s="11">
+        <v>4.2</v>
+      </c>
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
       <c r="W11" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="X11" s="14"/>
     </row>
@@ -4171,10 +4247,10 @@
         <v>327059552</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D12" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4183,7 +4259,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.95652173913043481</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
@@ -4193,16 +4269,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="11"/>
+      <c r="L12" s="11">
+        <v>11</v>
+      </c>
       <c r="M12" s="11"/>
       <c r="N12" s="2"/>
       <c r="O12" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P12" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.95652173913043481</v>
       </c>
       <c r="Q12" s="11">
         <v>0</v>
@@ -4215,7 +4293,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T12" s="11"/>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
       <c r="W12" s="14">
@@ -4229,14 +4309,14 @@
         <v>327017594</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D13" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="10">
@@ -4251,7 +4331,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L13" s="11"/>
+      <c r="L13" s="11">
+        <v>0</v>
+      </c>
       <c r="M13" s="11"/>
       <c r="N13" s="2"/>
       <c r="O13" s="11">
@@ -4273,7 +4355,9 @@
         <f t="shared" si="5"/>
         <v>0.46499999999999997</v>
       </c>
-      <c r="T13" s="11"/>
+      <c r="T13" s="11">
+        <v>0</v>
+      </c>
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
       <c r="W13" s="14">
@@ -4282,15 +4366,15 @@
       </c>
       <c r="X13" s="14"/>
     </row>
-    <row r="14" spans="1:24" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>327184481</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D14" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4299,7 +4383,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="10">
         <f t="shared" si="1"/>
-        <v>1.4549999999999998</v>
+        <v>4.1741304347826089</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
@@ -4309,16 +4393,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="11"/>
+      <c r="L14" s="11">
+        <v>20</v>
+      </c>
       <c r="M14" s="11"/>
       <c r="N14" s="2"/>
       <c r="O14" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P14" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.7391304347826086</v>
       </c>
       <c r="Q14" s="11">
         <v>9.6999999999999993</v>
@@ -4331,12 +4417,14 @@
         <f t="shared" si="5"/>
         <v>1.4549999999999998</v>
       </c>
-      <c r="T14" s="11"/>
+      <c r="T14" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
       <c r="W14" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="X14" s="14"/>
     </row>
@@ -4345,19 +4433,19 @@
         <v>327325862</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D15" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.0234782608695654</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
@@ -4367,16 +4455,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L15" s="11"/>
+      <c r="L15" s="11">
+        <v>12</v>
+      </c>
       <c r="M15" s="11"/>
       <c r="N15" s="2"/>
       <c r="O15" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P15" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.0434782608695652</v>
       </c>
       <c r="Q15" s="11">
         <v>0</v>
@@ -4389,12 +4479,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T15" s="11"/>
+      <c r="T15" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
       <c r="W15" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="X15" s="14"/>
     </row>
@@ -4403,10 +4495,10 @@
         <v>327180672</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D16" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4415,7 +4507,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="10">
         <f t="shared" si="1"/>
-        <v>0.40500000000000003</v>
+        <v>2.1441304347826087</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
@@ -4425,16 +4517,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L16" s="11"/>
+      <c r="L16" s="11">
+        <v>20</v>
+      </c>
       <c r="M16" s="11"/>
       <c r="N16" s="2"/>
       <c r="O16" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P16" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.7391304347826086</v>
       </c>
       <c r="Q16" s="11">
         <v>2.7</v>
@@ -4447,7 +4541,9 @@
         <f t="shared" si="5"/>
         <v>0.40500000000000003</v>
       </c>
-      <c r="T16" s="11"/>
+      <c r="T16" s="11">
+        <v>0</v>
+      </c>
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
       <c r="W16" s="14">
@@ -4461,10 +4557,10 @@
         <v>327147057</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D17" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4473,7 +4569,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="10">
         <f t="shared" si="1"/>
-        <v>0.54</v>
+        <v>3.2591304347826084</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
@@ -4483,16 +4579,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L17" s="11"/>
+      <c r="L17" s="11">
+        <v>20</v>
+      </c>
       <c r="M17" s="11"/>
       <c r="N17" s="2"/>
       <c r="O17" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P17" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.7391304347826086</v>
       </c>
       <c r="Q17" s="11">
         <v>3.6</v>
@@ -4505,12 +4603,14 @@
         <f t="shared" si="5"/>
         <v>0.54</v>
       </c>
-      <c r="T17" s="11"/>
+      <c r="T17" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="U17" s="11"/>
       <c r="V17" s="11"/>
       <c r="W17" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="X17" s="14"/>
     </row>
@@ -4519,10 +4619,10 @@
         <v>327194381</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D18" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4531,7 +4631,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="10">
         <f t="shared" si="1"/>
-        <v>0.28499999999999998</v>
+        <v>3.4510869565217392</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
@@ -4541,16 +4641,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="11"/>
+      <c r="L18" s="11">
+        <v>21</v>
+      </c>
       <c r="M18" s="11"/>
       <c r="N18" s="2"/>
       <c r="O18" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P18" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.826086956521739</v>
       </c>
       <c r="Q18" s="11">
         <v>1.9</v>
@@ -4563,12 +4665,14 @@
         <f t="shared" si="5"/>
         <v>0.28499999999999998</v>
       </c>
-      <c r="T18" s="11"/>
+      <c r="T18" s="11">
+        <v>6.7</v>
+      </c>
       <c r="U18" s="11"/>
       <c r="V18" s="11"/>
       <c r="W18" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X18" s="14"/>
     </row>
@@ -4577,10 +4681,10 @@
         <v>327233785</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D19" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4589,7 +4693,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="10">
         <f t="shared" si="1"/>
-        <v>0.61499999999999988</v>
+        <v>3.2810869565217393</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
@@ -4599,16 +4703,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L19" s="11"/>
+      <c r="L19" s="11">
+        <v>21</v>
+      </c>
       <c r="M19" s="11"/>
       <c r="N19" s="2"/>
       <c r="O19" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P19" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.826086956521739</v>
       </c>
       <c r="Q19" s="11">
         <v>4.0999999999999996</v>
@@ -4621,12 +4727,14 @@
         <f t="shared" si="5"/>
         <v>0.61499999999999988</v>
       </c>
-      <c r="T19" s="11"/>
+      <c r="T19" s="11">
+        <v>4.2</v>
+      </c>
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
       <c r="W19" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="X19" s="14"/>
     </row>
@@ -4635,19 +4743,19 @@
         <v>327276843</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D20" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="10">
         <f t="shared" si="1"/>
-        <v>0.54</v>
+        <v>2.5634782608695654</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
@@ -4657,16 +4765,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L20" s="11"/>
+      <c r="L20" s="11">
+        <v>12</v>
+      </c>
       <c r="M20" s="11"/>
       <c r="N20" s="2"/>
       <c r="O20" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P20" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.0434782608695652</v>
       </c>
       <c r="Q20" s="11">
         <v>3.6</v>
@@ -4679,12 +4789,14 @@
         <f t="shared" si="5"/>
         <v>0.54</v>
       </c>
-      <c r="T20" s="11"/>
+      <c r="T20" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
       <c r="W20" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.98000000000000009</v>
       </c>
       <c r="X20" s="14"/>
     </row>
@@ -4693,10 +4805,10 @@
         <v>327021650</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D21" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4705,7 +4817,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.6443478260869568</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
@@ -4715,16 +4827,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L21" s="11"/>
+      <c r="L21" s="11">
+        <v>15</v>
+      </c>
       <c r="M21" s="11"/>
       <c r="N21" s="2"/>
       <c r="O21" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P21" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.3043478260869565</v>
       </c>
       <c r="Q21" s="11">
         <v>0</v>
@@ -4737,12 +4851,14 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T21" s="11"/>
+      <c r="T21" s="11">
+        <v>6.7</v>
+      </c>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
       <c r="W21" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X21" s="14"/>
     </row>
@@ -4751,19 +4867,19 @@
         <v>327328557</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D22" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2173913043478262</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
@@ -4773,16 +4889,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L22" s="11"/>
+      <c r="L22" s="11">
+        <v>14</v>
+      </c>
       <c r="M22" s="11"/>
       <c r="N22" s="2"/>
       <c r="O22" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P22" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2173913043478262</v>
       </c>
       <c r="Q22" s="11">
         <v>0</v>
@@ -4795,7 +4913,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T22" s="11"/>
+      <c r="T22" s="11">
+        <v>0</v>
+      </c>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
       <c r="W22" s="14">
@@ -4809,10 +4929,10 @@
         <v>327073240</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D23" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4821,7 +4941,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.3043478260869565</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
@@ -4831,16 +4951,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L23" s="11"/>
+      <c r="L23" s="11">
+        <v>15</v>
+      </c>
       <c r="M23" s="11"/>
       <c r="N23" s="2"/>
       <c r="O23" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P23" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.3043478260869565</v>
       </c>
       <c r="Q23" s="11">
         <v>0</v>
@@ -4853,7 +4975,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T23" s="11"/>
+      <c r="T23" s="11">
+        <v>0</v>
+      </c>
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
       <c r="W23" s="14">
@@ -4867,19 +4991,19 @@
         <v>327167730</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D24" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="10">
         <f t="shared" si="1"/>
-        <v>0.18</v>
+        <v>2.4982608695652173</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
@@ -4889,16 +5013,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L24" s="11"/>
+      <c r="L24" s="11">
+        <v>17</v>
+      </c>
       <c r="M24" s="11"/>
       <c r="N24" s="2"/>
       <c r="O24" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P24" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.4782608695652173</v>
       </c>
       <c r="Q24" s="11">
         <v>1.2</v>
@@ -4911,12 +5037,14 @@
         <f t="shared" si="5"/>
         <v>0.18</v>
       </c>
-      <c r="T24" s="11"/>
+      <c r="T24" s="11">
+        <v>4.2</v>
+      </c>
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
       <c r="W24" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="X24" s="14"/>
     </row>
@@ -4925,10 +5053,10 @@
         <v>327182281</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D25" s="8">
         <f>Tabla1[[#This Row],[Porcentaje de Asistencia]]</f>
@@ -4937,7 +5065,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="10">
         <f t="shared" si="1"/>
-        <v>0.54</v>
+        <v>1.6704347826086956</v>
       </c>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
@@ -4947,16 +5075,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L25" s="11"/>
+      <c r="L25" s="11">
+        <v>13</v>
+      </c>
       <c r="M25" s="11"/>
       <c r="N25" s="2"/>
       <c r="O25" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P25" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.1304347826086956</v>
       </c>
       <c r="Q25" s="11">
         <v>3.6</v>
@@ -4969,7 +5099,9 @@
         <f t="shared" si="5"/>
         <v>0.54</v>
       </c>
-      <c r="T25" s="11"/>
+      <c r="T25" s="11">
+        <v>0</v>
+      </c>
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
       <c r="W25" s="14">
@@ -5092,7 +5224,7 @@
       </c>
       <c r="F36" s="17">
         <f>AVERAGE(F2:F25)</f>
-        <v>0.51687500000000008</v>
+        <v>2.5058967391304345</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
@@ -5364,20 +5496,7 @@
       <c r="W45" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X25" xr:uid="{2D94412C-462B-45A3-87AD-34BA6A5C5B8A}">
-    <filterColumn colId="16">
-      <filters>
-        <filter val="0"/>
-        <filter val="1.2"/>
-        <filter val="1.9"/>
-        <filter val="2.7"/>
-        <filter val="3.1"/>
-        <filter val="3.6"/>
-        <filter val="4.1"/>
-        <filter val="5.3"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:X25" xr:uid="{2D94412C-462B-45A3-87AD-34BA6A5C5B8A}"/>
   <conditionalFormatting sqref="F2:F25">
     <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="NP">
       <formula>NOT(ISERROR(SEARCH("NP",F2)))</formula>
@@ -5400,7 +5519,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF9BAA56-82DB-4C0B-9E50-A99B3B9393AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF9BAA56-82DB-4C0B-9E50-A99B3B9393AC}">
   <dimension ref="A1:DW50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5409,12 +5528,12 @@
     <col min="3" max="3" width="11.54296875" customWidth="1"/>
     <col min="4" max="4" width="13.7265625" style="26" hidden="1" customWidth="1"/>
     <col min="5" max="7" width="10.7265625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="12" width="0" hidden="1" customWidth="1"/>
     <col min="107" max="108" width="11.54296875" customWidth="1"/>
     <col min="109" max="109" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:127" ht="21.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:127" ht="22" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
         <v>31</v>
       </c>
@@ -5425,322 +5544,322 @@
         <v>33</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E1" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="J1" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="K1" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="L1" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="M1" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="N1" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="O1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="P1" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="Q1" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="R1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="S1" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="T1" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="U1" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="R1" s="23" t="s">
+      <c r="V1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="W1" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="T1" s="23" t="s">
+      <c r="X1" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="U1" s="23" t="s">
+      <c r="Y1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="V1" s="23" t="s">
+      <c r="Z1" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="W1" s="23" t="s">
+      <c r="AA1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="X1" s="23" t="s">
+      <c r="AB1" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="Y1" s="23" t="s">
+      <c r="AC1" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="Z1" s="23" t="s">
+      <c r="AD1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="AA1" s="23" t="s">
+      <c r="AE1" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="AB1" s="23" t="s">
+      <c r="AF1" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AC1" s="23" t="s">
+      <c r="AG1" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="AD1" s="23" t="s">
+      <c r="AH1" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="AE1" s="23" t="s">
+      <c r="AI1" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="AF1" s="23" t="s">
+      <c r="AJ1" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="AG1" s="23" t="s">
+      <c r="AK1" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="AH1" s="23" t="s">
+      <c r="AL1" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="AI1" s="23" t="s">
+      <c r="AM1" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="AJ1" s="23" t="s">
+      <c r="AN1" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="AK1" s="23" t="s">
+      <c r="AO1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AL1" s="23" t="s">
+      <c r="AP1" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="AM1" s="23" t="s">
+      <c r="AQ1" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="AN1" s="23" t="s">
+      <c r="AR1" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="AO1" s="23" t="s">
+      <c r="AS1" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="AP1" s="23" t="s">
+      <c r="AT1" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="AQ1" s="23" t="s">
+      <c r="AU1" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="AR1" s="23" t="s">
+      <c r="AV1" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="AS1" s="23" t="s">
+      <c r="AW1" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="AT1" s="23" t="s">
+      <c r="AX1" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AU1" s="23" t="s">
+      <c r="AY1" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="AV1" s="23" t="s">
+      <c r="AZ1" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="AW1" s="23" t="s">
+      <c r="BA1" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="AX1" s="23" t="s">
+      <c r="BB1" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="AY1" s="23" t="s">
+      <c r="BC1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="AZ1" s="23" t="s">
+      <c r="BD1" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="BA1" s="23" t="s">
+      <c r="BE1" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="BB1" s="23" t="s">
+      <c r="BF1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="BC1" s="23" t="s">
+      <c r="BG1" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="BD1" s="23" t="s">
+      <c r="BH1" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="BE1" s="23" t="s">
+      <c r="BI1" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="BF1" s="23" t="s">
+      <c r="BJ1" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="BG1" s="23" t="s">
+      <c r="BK1" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="BH1" s="23" t="s">
+      <c r="BL1" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="BI1" s="23" t="s">
+      <c r="BM1" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="BJ1" s="23" t="s">
+      <c r="BN1" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="BK1" s="23" t="s">
+      <c r="BO1" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="BL1" s="23" t="s">
+      <c r="BP1" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="BM1" s="23" t="s">
+      <c r="BQ1" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="BN1" s="23" t="s">
+      <c r="BR1" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="BO1" s="23" t="s">
+      <c r="BS1" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="BP1" s="23" t="s">
+      <c r="BT1" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="BQ1" s="23" t="s">
+      <c r="BU1" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="BR1" s="23" t="s">
+      <c r="BV1" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="BS1" s="23" t="s">
+      <c r="BW1" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="BT1" s="23" t="s">
+      <c r="BX1" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="BU1" s="23" t="s">
+      <c r="BY1" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="BV1" s="23" t="s">
+      <c r="BZ1" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="BW1" s="23" t="s">
+      <c r="CA1" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="BX1" s="23" t="s">
+      <c r="CB1" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="BY1" s="23" t="s">
+      <c r="CC1" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="BZ1" s="23" t="s">
+      <c r="CD1" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="CA1" s="23" t="s">
+      <c r="CE1" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="CB1" s="23" t="s">
+      <c r="CF1" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="CC1" s="23" t="s">
+      <c r="CG1" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="CD1" s="23" t="s">
+      <c r="CH1" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="CE1" s="23" t="s">
+      <c r="CI1" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="CF1" s="23" t="s">
+      <c r="CJ1" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="CG1" s="23" t="s">
+      <c r="CK1" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="CH1" s="23" t="s">
+      <c r="CL1" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="CI1" s="23" t="s">
+      <c r="CM1" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="CJ1" s="23" t="s">
+      <c r="CN1" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CK1" s="23" t="s">
+      <c r="CO1" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="CL1" s="23" t="s">
+      <c r="CP1" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="CM1" s="23" t="s">
+      <c r="CQ1" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="CN1" s="23" t="s">
+      <c r="CR1" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="CO1" s="23" t="s">
+      <c r="CS1" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="CP1" s="23" t="s">
+      <c r="CT1" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="CQ1" s="23" t="s">
+      <c r="CU1" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="CR1" s="23" t="s">
+      <c r="CV1" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="CS1" s="23" t="s">
+      <c r="CW1" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="CT1" s="23" t="s">
+      <c r="CX1" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="CU1" s="23" t="s">
+      <c r="CY1" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="CV1" s="23" t="s">
+      <c r="CZ1" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="CW1" s="23" t="s">
+      <c r="DA1" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="CX1" s="23" t="s">
+      <c r="DB1" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="CY1" s="23" t="s">
+      <c r="DC1" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="CZ1" s="23" t="s">
+      <c r="DD1" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="DA1" s="23" t="s">
+      <c r="DE1" s="22" t="s">
         <v>129</v>
-      </c>
-      <c r="DB1" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="DC1" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="DD1" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="DE1" s="22" t="s">
-        <v>133</v>
       </c>
       <c r="DF1" s="1"/>
       <c r="DG1" s="1"/>
@@ -5766,11 +5885,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C2" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D2" s="25">
         <v>1</v>
@@ -5787,11 +5906,21 @@
       <c r="H2" s="25">
         <v>1</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
+      <c r="I2" s="25">
+        <v>1</v>
+      </c>
+      <c r="J2" s="25">
+        <v>2</v>
+      </c>
+      <c r="K2" s="25">
+        <v>1</v>
+      </c>
+      <c r="L2" s="25">
+        <v>1</v>
+      </c>
+      <c r="M2" s="25">
+        <v>2</v>
+      </c>
       <c r="N2" s="25"/>
       <c r="O2" s="25"/>
       <c r="P2" s="25"/>
@@ -5889,7 +6018,7 @@
       <c r="DD2" s="25"/>
       <c r="DE2" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DF2" s="1"/>
       <c r="DG2" s="1"/>
@@ -5915,7 +6044,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C3" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -5936,11 +6065,21 @@
       <c r="H3" s="25">
         <v>1</v>
       </c>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
+      <c r="I3" s="25">
+        <v>1</v>
+      </c>
+      <c r="J3" s="25">
+        <v>1</v>
+      </c>
+      <c r="K3" s="25">
+        <v>1</v>
+      </c>
+      <c r="L3" s="25">
+        <v>1</v>
+      </c>
+      <c r="M3" s="25">
+        <v>1</v>
+      </c>
       <c r="N3" s="25"/>
       <c r="O3" s="25"/>
       <c r="P3" s="25"/>
@@ -6038,7 +6177,7 @@
       <c r="DD3" s="25"/>
       <c r="DE3" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF3" s="1"/>
       <c r="DG3" s="1"/>
@@ -6064,11 +6203,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C4" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D4" s="25">
         <v>1</v>
@@ -6085,11 +6224,21 @@
       <c r="H4" s="25">
         <v>1</v>
       </c>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="I4" s="25">
+        <v>1</v>
+      </c>
+      <c r="J4" s="25">
+        <v>2</v>
+      </c>
+      <c r="K4" s="25">
+        <v>1</v>
+      </c>
+      <c r="L4" s="25">
+        <v>2</v>
+      </c>
+      <c r="M4" s="25">
+        <v>2</v>
+      </c>
       <c r="N4" s="25"/>
       <c r="O4" s="25"/>
       <c r="P4" s="25"/>
@@ -6187,7 +6336,7 @@
       <c r="DD4" s="25"/>
       <c r="DE4" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="DF4" s="1"/>
       <c r="DG4" s="1"/>
@@ -6213,7 +6362,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C5" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -6234,11 +6383,21 @@
       <c r="H5" s="25">
         <v>1</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
+      <c r="I5" s="25">
+        <v>1</v>
+      </c>
+      <c r="J5" s="25">
+        <v>1</v>
+      </c>
+      <c r="K5" s="25">
+        <v>1</v>
+      </c>
+      <c r="L5" s="25">
+        <v>1</v>
+      </c>
+      <c r="M5" s="25">
+        <v>1</v>
+      </c>
       <c r="N5" s="25"/>
       <c r="O5" s="25"/>
       <c r="P5" s="25"/>
@@ -6336,7 +6495,7 @@
       <c r="DD5" s="25"/>
       <c r="DE5" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF5" s="1"/>
       <c r="DG5" s="1"/>
@@ -6362,11 +6521,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C6" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D6" s="25">
         <v>1</v>
@@ -6383,11 +6542,21 @@
       <c r="H6" s="25">
         <v>1</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
+      <c r="I6" s="25">
+        <v>2</v>
+      </c>
+      <c r="J6" s="25">
+        <v>2</v>
+      </c>
+      <c r="K6" s="25">
+        <v>1</v>
+      </c>
+      <c r="L6" s="25">
+        <v>1</v>
+      </c>
+      <c r="M6" s="25">
+        <v>2</v>
+      </c>
       <c r="N6" s="25"/>
       <c r="O6" s="25"/>
       <c r="P6" s="25"/>
@@ -6485,7 +6654,7 @@
       <c r="DD6" s="25"/>
       <c r="DE6" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DF6" s="1"/>
       <c r="DG6" s="1"/>
@@ -6511,7 +6680,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C7" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -6532,11 +6701,21 @@
       <c r="H7" s="25">
         <v>1</v>
       </c>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
+      <c r="I7" s="25">
+        <v>1</v>
+      </c>
+      <c r="J7" s="25">
+        <v>1</v>
+      </c>
+      <c r="K7" s="25">
+        <v>1</v>
+      </c>
+      <c r="L7" s="25">
+        <v>1</v>
+      </c>
+      <c r="M7" s="25">
+        <v>1</v>
+      </c>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
       <c r="P7" s="25"/>
@@ -6634,7 +6813,7 @@
       <c r="DD7" s="25"/>
       <c r="DE7" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF7" s="1"/>
       <c r="DG7" s="1"/>
@@ -6660,7 +6839,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C8" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -6681,11 +6860,21 @@
       <c r="H8" s="25">
         <v>1</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
+      <c r="I8" s="25">
+        <v>1</v>
+      </c>
+      <c r="J8" s="25">
+        <v>1</v>
+      </c>
+      <c r="K8" s="25">
+        <v>1</v>
+      </c>
+      <c r="L8" s="25">
+        <v>1</v>
+      </c>
+      <c r="M8" s="25">
+        <v>1</v>
+      </c>
       <c r="N8" s="25"/>
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
@@ -6783,7 +6972,7 @@
       <c r="DD8" s="25"/>
       <c r="DE8" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF8" s="1"/>
       <c r="DG8" s="1"/>
@@ -6809,11 +6998,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C9" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D9" s="25">
         <v>1</v>
@@ -6830,11 +7019,21 @@
       <c r="H9" s="25">
         <v>1</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
+      <c r="I9" s="25">
+        <v>1</v>
+      </c>
+      <c r="J9" s="25">
+        <v>2</v>
+      </c>
+      <c r="K9" s="25">
+        <v>1</v>
+      </c>
+      <c r="L9" s="25">
+        <v>1</v>
+      </c>
+      <c r="M9" s="25">
+        <v>1</v>
+      </c>
       <c r="N9" s="25"/>
       <c r="O9" s="25"/>
       <c r="P9" s="25"/>
@@ -6932,7 +7131,7 @@
       <c r="DD9" s="25"/>
       <c r="DE9" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="DF9" s="1"/>
       <c r="DG9" s="1"/>
@@ -6958,11 +7157,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C10" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D10" s="25">
         <v>1</v>
@@ -6979,11 +7178,21 @@
       <c r="H10" s="25">
         <v>1</v>
       </c>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
+      <c r="I10" s="25">
+        <v>1</v>
+      </c>
+      <c r="J10" s="25">
+        <v>2</v>
+      </c>
+      <c r="K10" s="25">
+        <v>1</v>
+      </c>
+      <c r="L10" s="25">
+        <v>1</v>
+      </c>
+      <c r="M10" s="25">
+        <v>1</v>
+      </c>
       <c r="N10" s="25"/>
       <c r="O10" s="25"/>
       <c r="P10" s="25"/>
@@ -7081,7 +7290,7 @@
       <c r="DD10" s="25"/>
       <c r="DE10" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="DF10" s="1"/>
       <c r="DG10" s="1"/>
@@ -7107,11 +7316,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C11" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D11" s="25">
         <v>1</v>
@@ -7128,11 +7337,21 @@
       <c r="H11" s="25">
         <v>1</v>
       </c>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
+      <c r="I11" s="25">
+        <v>2</v>
+      </c>
+      <c r="J11" s="25">
+        <v>1</v>
+      </c>
+      <c r="K11" s="25">
+        <v>1</v>
+      </c>
+      <c r="L11" s="25">
+        <v>1</v>
+      </c>
+      <c r="M11" s="25">
+        <v>2</v>
+      </c>
       <c r="N11" s="25"/>
       <c r="O11" s="25"/>
       <c r="P11" s="25"/>
@@ -7230,7 +7449,7 @@
       <c r="DD11" s="25"/>
       <c r="DE11" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DF11" s="1"/>
       <c r="DG11" s="1"/>
@@ -7256,7 +7475,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C12" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -7277,11 +7496,21 @@
       <c r="H12" s="25">
         <v>1</v>
       </c>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
+      <c r="I12" s="25">
+        <v>1</v>
+      </c>
+      <c r="J12" s="25">
+        <v>1</v>
+      </c>
+      <c r="K12" s="25">
+        <v>1</v>
+      </c>
+      <c r="L12" s="25">
+        <v>1</v>
+      </c>
+      <c r="M12" s="25">
+        <v>1</v>
+      </c>
       <c r="N12" s="25"/>
       <c r="O12" s="25"/>
       <c r="P12" s="25"/>
@@ -7379,7 +7608,7 @@
       <c r="DD12" s="25"/>
       <c r="DE12" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF12" s="1"/>
       <c r="DG12" s="1"/>
@@ -7405,11 +7634,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C13" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D13" s="25">
         <v>2</v>
@@ -7426,11 +7655,21 @@
       <c r="H13" s="25">
         <v>1</v>
       </c>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
+      <c r="I13" s="25">
+        <v>1</v>
+      </c>
+      <c r="J13" s="25">
+        <v>1</v>
+      </c>
+      <c r="K13" s="25">
+        <v>1</v>
+      </c>
+      <c r="L13" s="25">
+        <v>1</v>
+      </c>
+      <c r="M13" s="25">
+        <v>1</v>
+      </c>
       <c r="N13" s="25"/>
       <c r="O13" s="25"/>
       <c r="P13" s="25"/>
@@ -7528,7 +7767,7 @@
       <c r="DD13" s="25"/>
       <c r="DE13" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="DF13" s="1"/>
       <c r="DG13" s="1"/>
@@ -7554,7 +7793,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C14" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -7575,11 +7814,21 @@
       <c r="H14" s="25">
         <v>1</v>
       </c>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
+      <c r="I14" s="25">
+        <v>1</v>
+      </c>
+      <c r="J14" s="25">
+        <v>1</v>
+      </c>
+      <c r="K14" s="25">
+        <v>1</v>
+      </c>
+      <c r="L14" s="25">
+        <v>1</v>
+      </c>
+      <c r="M14" s="25">
+        <v>1</v>
+      </c>
       <c r="N14" s="25"/>
       <c r="O14" s="25"/>
       <c r="P14" s="25"/>
@@ -7677,7 +7926,7 @@
       <c r="DD14" s="25"/>
       <c r="DE14" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF14" s="1"/>
       <c r="DG14" s="1"/>
@@ -7703,11 +7952,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C15" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D15" s="25">
         <v>1</v>
@@ -7724,11 +7973,21 @@
       <c r="H15" s="25">
         <v>1</v>
       </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
+      <c r="I15" s="25">
+        <v>1</v>
+      </c>
+      <c r="J15" s="25">
+        <v>1</v>
+      </c>
+      <c r="K15" s="25">
+        <v>1</v>
+      </c>
+      <c r="L15" s="25">
+        <v>1</v>
+      </c>
+      <c r="M15" s="25">
+        <v>2</v>
+      </c>
       <c r="N15" s="25"/>
       <c r="O15" s="25"/>
       <c r="P15" s="25"/>
@@ -7826,7 +8085,7 @@
       <c r="DD15" s="25"/>
       <c r="DE15" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="DF15" s="1"/>
       <c r="DG15" s="1"/>
@@ -7852,7 +8111,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C16" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -7873,11 +8132,21 @@
       <c r="H16" s="25">
         <v>1</v>
       </c>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
+      <c r="I16" s="25">
+        <v>1</v>
+      </c>
+      <c r="J16" s="25">
+        <v>1</v>
+      </c>
+      <c r="K16" s="25">
+        <v>1</v>
+      </c>
+      <c r="L16" s="25">
+        <v>1</v>
+      </c>
+      <c r="M16" s="25">
+        <v>1</v>
+      </c>
       <c r="N16" s="25"/>
       <c r="O16" s="25"/>
       <c r="P16" s="25"/>
@@ -7975,7 +8244,7 @@
       <c r="DD16" s="25"/>
       <c r="DE16" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF16" s="1"/>
       <c r="DG16" s="1"/>
@@ -8001,7 +8270,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C17" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -8022,11 +8291,21 @@
       <c r="H17" s="25">
         <v>1</v>
       </c>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
+      <c r="I17" s="25">
+        <v>1</v>
+      </c>
+      <c r="J17" s="25">
+        <v>1</v>
+      </c>
+      <c r="K17" s="25">
+        <v>1</v>
+      </c>
+      <c r="L17" s="25">
+        <v>1</v>
+      </c>
+      <c r="M17" s="25">
+        <v>1</v>
+      </c>
       <c r="N17" s="25"/>
       <c r="O17" s="25"/>
       <c r="P17" s="25"/>
@@ -8124,7 +8403,7 @@
       <c r="DD17" s="25"/>
       <c r="DE17" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF17" s="1"/>
       <c r="DG17" s="1"/>
@@ -8150,7 +8429,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C18" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -8171,11 +8450,21 @@
       <c r="H18" s="25">
         <v>1</v>
       </c>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
+      <c r="I18" s="25">
+        <v>1</v>
+      </c>
+      <c r="J18" s="25">
+        <v>1</v>
+      </c>
+      <c r="K18" s="25">
+        <v>1</v>
+      </c>
+      <c r="L18" s="25">
+        <v>1</v>
+      </c>
+      <c r="M18" s="25">
+        <v>1</v>
+      </c>
       <c r="N18" s="25"/>
       <c r="O18" s="25"/>
       <c r="P18" s="25"/>
@@ -8273,7 +8562,7 @@
       <c r="DD18" s="25"/>
       <c r="DE18" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF18" s="1"/>
       <c r="DG18" s="1"/>
@@ -8299,7 +8588,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C19" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -8320,11 +8609,21 @@
       <c r="H19" s="25">
         <v>1</v>
       </c>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
+      <c r="I19" s="25">
+        <v>1</v>
+      </c>
+      <c r="J19" s="25">
+        <v>1</v>
+      </c>
+      <c r="K19" s="25">
+        <v>1</v>
+      </c>
+      <c r="L19" s="25">
+        <v>1</v>
+      </c>
+      <c r="M19" s="25">
+        <v>1</v>
+      </c>
       <c r="N19" s="25"/>
       <c r="O19" s="25"/>
       <c r="P19" s="25"/>
@@ -8422,7 +8721,7 @@
       <c r="DD19" s="25"/>
       <c r="DE19" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF19" s="1"/>
       <c r="DG19" s="1"/>
@@ -8448,11 +8747,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C20" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D20" s="25">
         <v>1</v>
@@ -8469,11 +8768,21 @@
       <c r="H20" s="25">
         <v>1</v>
       </c>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
+      <c r="I20" s="25">
+        <v>1</v>
+      </c>
+      <c r="J20" s="25">
+        <v>2</v>
+      </c>
+      <c r="K20" s="25">
+        <v>1</v>
+      </c>
+      <c r="L20" s="25">
+        <v>1</v>
+      </c>
+      <c r="M20" s="25">
+        <v>2</v>
+      </c>
       <c r="N20" s="25"/>
       <c r="O20" s="25"/>
       <c r="P20" s="25"/>
@@ -8571,7 +8880,7 @@
       <c r="DD20" s="25"/>
       <c r="DE20" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DF20" s="1"/>
       <c r="DG20" s="1"/>
@@ -8597,7 +8906,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C21" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -8618,11 +8927,21 @@
       <c r="H21" s="25">
         <v>1</v>
       </c>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
+      <c r="I21" s="25">
+        <v>1</v>
+      </c>
+      <c r="J21" s="25">
+        <v>1</v>
+      </c>
+      <c r="K21" s="25">
+        <v>1</v>
+      </c>
+      <c r="L21" s="25">
+        <v>1</v>
+      </c>
+      <c r="M21" s="25">
+        <v>1</v>
+      </c>
       <c r="N21" s="25"/>
       <c r="O21" s="25"/>
       <c r="P21" s="25"/>
@@ -8720,7 +9039,7 @@
       <c r="DD21" s="25"/>
       <c r="DE21" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF21" s="1"/>
       <c r="DG21" s="1"/>
@@ -8746,11 +9065,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C22" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D22" s="25">
         <v>1</v>
@@ -8767,11 +9086,21 @@
       <c r="H22" s="25">
         <v>1</v>
       </c>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
+      <c r="I22" s="25">
+        <v>1</v>
+      </c>
+      <c r="J22" s="25">
+        <v>2</v>
+      </c>
+      <c r="K22" s="25">
+        <v>1</v>
+      </c>
+      <c r="L22" s="25">
+        <v>1</v>
+      </c>
+      <c r="M22" s="25">
+        <v>2</v>
+      </c>
       <c r="N22" s="25"/>
       <c r="O22" s="25"/>
       <c r="P22" s="25"/>
@@ -8869,7 +9198,7 @@
       <c r="DD22" s="25"/>
       <c r="DE22" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DF22" s="1"/>
       <c r="DG22" s="1"/>
@@ -8895,7 +9224,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C23" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -8916,11 +9245,21 @@
       <c r="H23" s="25">
         <v>1</v>
       </c>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
+      <c r="I23" s="25">
+        <v>1</v>
+      </c>
+      <c r="J23" s="25">
+        <v>1</v>
+      </c>
+      <c r="K23" s="25">
+        <v>1</v>
+      </c>
+      <c r="L23" s="25">
+        <v>1</v>
+      </c>
+      <c r="M23" s="25">
+        <v>1</v>
+      </c>
       <c r="N23" s="25"/>
       <c r="O23" s="25"/>
       <c r="P23" s="25"/>
@@ -9018,7 +9357,7 @@
       <c r="DD23" s="25"/>
       <c r="DE23" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF23" s="1"/>
       <c r="DG23" s="1"/>
@@ -9044,11 +9383,11 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C24" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D24" s="25">
         <v>1</v>
@@ -9065,11 +9404,21 @@
       <c r="H24" s="25">
         <v>1</v>
       </c>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
+      <c r="I24" s="25">
+        <v>1</v>
+      </c>
+      <c r="J24" s="25">
+        <v>2</v>
+      </c>
+      <c r="K24" s="25">
+        <v>1</v>
+      </c>
+      <c r="L24" s="25">
+        <v>1</v>
+      </c>
+      <c r="M24" s="25">
+        <v>2</v>
+      </c>
       <c r="N24" s="25"/>
       <c r="O24" s="25"/>
       <c r="P24" s="25"/>
@@ -9167,7 +9516,7 @@
       <c r="DD24" s="25"/>
       <c r="DE24" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DF24" s="1"/>
       <c r="DG24" s="1"/>
@@ -9193,7 +9542,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C25" s="24">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])/COUNTA(Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
@@ -9214,11 +9563,21 @@
       <c r="H25" s="25">
         <v>1</v>
       </c>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
+      <c r="I25" s="25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="25">
+        <v>1</v>
+      </c>
+      <c r="K25" s="25">
+        <v>1</v>
+      </c>
+      <c r="L25" s="25">
+        <v>1</v>
+      </c>
+      <c r="M25" s="25">
+        <v>1</v>
+      </c>
       <c r="N25" s="25"/>
       <c r="O25" s="25"/>
       <c r="P25" s="25"/>
@@ -9316,7 +9675,7 @@
       <c r="DD25" s="25"/>
       <c r="DE25" s="2">
         <f>SUMIF(Tabla1[[#This Row],[Khan Academy]:[Columna11]], 1,Tabla1[[#This Row],[Khan Academy]:[Columna11]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="DF25" s="1"/>
       <c r="DG25" s="1"/>
@@ -9337,7 +9696,7 @@
       <c r="DV25" s="1"/>
       <c r="DW25" s="1"/>
     </row>
-    <row r="26" spans="1:127" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:127" ht="64" x14ac:dyDescent="0.35">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="2"/>
@@ -9349,7 +9708,9 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+      <c r="M26" s="22" t="s">
+        <v>193</v>
+      </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -12553,8 +12914,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
